--- a/dt_dalali_ecommerce/system_items_analysis/item_groups_With_public_Images.xlsx
+++ b/dt_dalali_ecommerce/system_items_analysis/item_groups_With_public_Images.xlsx
@@ -175,10 +175,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -214,6 +214,44 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -222,6 +260,35 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -237,46 +304,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -290,70 +334,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -366,181 +366,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -564,22 +564,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,6 +599,41 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -631,26 +651,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -660,134 +660,134 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -795,10 +795,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1127,361 +1125,361 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="21" spans="1:4">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="2" t="b">
         <f t="shared" ref="C2:C24" si="0">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="A9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C10" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="A12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="A15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C16" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="4" t="s">
+      <c r="A18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C18" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="A19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C19" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="4" t="s">
+      <c r="A20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C20" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="4" t="s">
+      <c r="A21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="A22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C22" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="A23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="4" t="s">
+      <c r="A24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C24" s="2" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="2" t="s">
         <v>50</v>
       </c>
     </row>
